--- a/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
+++ b/KatalonData/ABPTestData/SchedulePaymentABP_DCF.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="167">
   <si>
     <t>Result</t>
   </si>
@@ -692,6 +692,66 @@
   </si>
   <si>
     <t>Fri Sep 18 01:32:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:03:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:18:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:22:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:26:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:29:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 18:53:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 19:21:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 19:27:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 19:31:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 24 19:38:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 15:42:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 18:45:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:03:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:15:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:23:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:28:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:32:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:57:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Sep 25 19:59:34 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1192,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1277,7 +1337,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>24</v>
@@ -1422,7 +1482,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1565,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1710,7 +1770,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1853,7 +1913,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -1998,7 +2058,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2141,7 +2201,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2286,7 +2346,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
@@ -2429,7 +2489,7 @@
         <v>14</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="5" t="s">
